--- a/artfynd/A 24339-2023 artfynd.xlsx
+++ b/artfynd/A 24339-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24339-2023 artfynd.xlsx
+++ b/artfynd/A 24339-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>29948</v>
+        <v>64255210</v>
       </c>
       <c r="B2" t="n">
-        <v>57149</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208260</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,16 +708,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Asa badplats, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487271.3044140592</v>
+        <v>487271</v>
       </c>
       <c r="R2" t="n">
-        <v>6335848.054063885</v>
+        <v>6335848</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -749,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-07-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,39 +776,34 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Persson</t>
+          <t>Mikael Persson, Therese Petersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64255258</v>
+        <v>64255315</v>
       </c>
       <c r="B3" t="n">
-        <v>55803</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102952</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,7 +813,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -842,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487271.3044140592</v>
+        <v>487271</v>
       </c>
       <c r="R3" t="n">
-        <v>6335848.054063885</v>
+        <v>6335848</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -875,19 +862,9 @@
           <t>2017-03-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-03-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,32 +891,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64255210</v>
+        <v>64255258</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,14 +921,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -965,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487271.3044140592</v>
+        <v>487271</v>
       </c>
       <c r="R4" t="n">
-        <v>6335848.054063885</v>
+        <v>6335848</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,19 +970,9 @@
           <t>2017-03-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-03-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,6 +996,215 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>64255186</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Asa badplats, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>487271</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6335848</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-03-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-03-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Persson, Therese Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>29948</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Asa badplats, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>487271</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6335848</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2010-07-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2010-07-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24339-2023 artfynd.xlsx
+++ b/artfynd/A 24339-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64255210</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64255315</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64255258</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64255186</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,8 +1230,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/29948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>